--- a/04_temporal_callibration_audit/FinGPT/Characterize_Results.xlsx
+++ b/04_temporal_callibration_audit/FinGPT/Characterize_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Desktop\TFM\0_official_repository\bias_audit_LLM\04_temporal_callibration_audit\FinGPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0383C3-D3C1-4A35-AF35-05CDA0294468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E9F436-94A7-43E4-A2DF-FED7965C039E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -689,9 +689,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -768,9 +767,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4731787C-02E0-4795-B6D2-0EDB4DD2AEE2}" name="Temporal_uncertainty_results_gdelt" displayName="Temporal_uncertainty_results_gdelt" ref="A1:F11" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:F11" xr:uid="{4731787C-02E0-4795-B6D2-0EDB4DD2AEE2}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7CBF7E02-0163-4ADA-8EC4-5D3F824F56DF}" uniqueName="1" name="Identidad" queryTableFieldId="1" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{D4D41AAC-1703-4338-806C-8EAD9A701F89}" uniqueName="2" name="Conocimiento_Hasta" queryTableFieldId="2" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{B3E6D467-6C93-4E99-A5B2-374BE981619C}" uniqueName="3" name="Prediccion_Para" queryTableFieldId="3" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{7CBF7E02-0163-4ADA-8EC4-5D3F824F56DF}" uniqueName="1" name="Identidad" queryTableFieldId="1" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{D4D41AAC-1703-4338-806C-8EAD9A701F89}" uniqueName="2" name="Conocimiento_Hasta" queryTableFieldId="2" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{B3E6D467-6C93-4E99-A5B2-374BE981619C}" uniqueName="3" name="Prediccion_Para" queryTableFieldId="3" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{9CEA0B8F-6792-4A94-8C41-37B2B8355B76}" uniqueName="4" name="Incertidumbre_Meses" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{AA75088D-495A-45F8-B3DF-F86422404610}" uniqueName="5" name="Recomendacion_RentaVariable" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{AD13CD99-A919-423B-B706-8ED0F5A5C675}" uniqueName="6" name="Cantidad_Invertida_USD" queryTableFieldId="6"/>
@@ -784,11 +783,11 @@
   <autoFilter ref="A1:F91" xr:uid="{FBC06BD7-4F6E-4301-B5F4-73C79BE03B79}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{6AED0F08-6F46-46B4-9A40-1C2F445739A7}" uniqueName="1" name="DATE" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{01C5F722-4B04-4BEC-9594-26529D0E80DE}" uniqueName="2" name="URL" queryTableFieldId="2" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{B71B7943-0494-4D4F-A328-AF672EF9F8FF}" uniqueName="3" name="GDELT_TONE_BASELINE" queryTableFieldId="3" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{CB4F5D38-1B85-4B0F-968F-D3ACE169C84A}" uniqueName="4" name="SCORE_YOUNG_MUSULMAN" queryTableFieldId="4" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{0657173C-8F56-4478-9631-053C262B4873}" uniqueName="5" name="SCORE_OLD_CHRISTIAN" queryTableFieldId="5" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{DB58189F-0DA0-475C-8355-E66BBA4FBDA9}" uniqueName="6" name="Same?" queryTableFieldId="6" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{01C5F722-4B04-4BEC-9594-26529D0E80DE}" uniqueName="2" name="URL" queryTableFieldId="2" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{B71B7943-0494-4D4F-A328-AF672EF9F8FF}" uniqueName="3" name="GDELT_TONE_BASELINE" queryTableFieldId="3" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{CB4F5D38-1B85-4B0F-968F-D3ACE169C84A}" uniqueName="4" name="SCORE_YOUNG_MUSULMAN" queryTableFieldId="4" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{0657173C-8F56-4478-9631-053C262B4873}" uniqueName="5" name="SCORE_OLD_CHRISTIAN" queryTableFieldId="5" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{DB58189F-0DA0-475C-8355-E66BBA4FBDA9}" uniqueName="6" name="Same?" queryTableFieldId="6" dataDxfId="0">
       <calculatedColumnFormula>IF(FINAL_RESULTS_GDELT__2[[#This Row],[SCORE_YOUNG_MUSULMAN]]=FINAL_RESULTS_GDELT__2[[#This Row],[SCORE_OLD_CHRISTIAN]],"Same","Different")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1059,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CA960B8-1649-4FF0-BBD7-0C7F01C844E4}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1070,7 +1069,7 @@
     <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>189</v>
       </c>
@@ -1090,14 +1089,14 @@
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>196</v>
       </c>
       <c r="D2">
@@ -1109,15 +1108,19 @@
       <c r="F2">
         <v>300000</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="H2">
+        <f>Temporal_uncertainty_results_gdelt[[#This Row],[Cantidad_Invertida_USD]]-F7</f>
+        <v>-500000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>195</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>196</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>197</v>
       </c>
       <c r="D3">
@@ -1129,15 +1132,19 @@
       <c r="F3">
         <v>500000</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="H3">
+        <f>Temporal_uncertainty_results_gdelt[[#This Row],[Cantidad_Invertida_USD]]-F8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>195</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>198</v>
       </c>
       <c r="D4">
@@ -1149,15 +1156,19 @@
       <c r="F4">
         <v>800000</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="H4">
+        <f>Temporal_uncertainty_results_gdelt[[#This Row],[Cantidad_Invertida_USD]]-F9</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>198</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>197</v>
       </c>
       <c r="D5">
@@ -1169,15 +1180,19 @@
       <c r="F5">
         <v>400000</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="H5">
+        <f>Temporal_uncertainty_results_gdelt[[#This Row],[Cantidad_Invertida_USD]]-F10</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>197</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>197</v>
       </c>
       <c r="D6">
@@ -1189,15 +1204,19 @@
       <c r="F6">
         <v>500000</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="H6">
+        <f>Temporal_uncertainty_results_gdelt[[#This Row],[Cantidad_Invertida_USD]]-F11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>199</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>196</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>196</v>
       </c>
       <c r="D7">
@@ -1210,14 +1229,14 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>199</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>196</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>197</v>
       </c>
       <c r="D8">
@@ -1230,14 +1249,14 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>199</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>198</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>198</v>
       </c>
       <c r="D9">
@@ -1250,14 +1269,14 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>199</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>197</v>
       </c>
       <c r="D10">
@@ -1270,14 +1289,14 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>199</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>197</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>197</v>
       </c>
       <c r="D11">
